--- a/reports/CLIC2027_de_xuat.xlsx
+++ b/reports/CLIC2027_de_xuat.xlsx
@@ -2116,7 +2116,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ảnh sơ đồ chi tiết: figures/drawio/1_kien_truc.drawio và 2_pipeline_ma_hoa_giai_ma.drawio</t>
+          <t>Ảnh sơ đồ chi tiết: paper/figures/drawio/1_kien_truc.drawio và 2_pipeline_ma_hoa_giai_ma.drawio</t>
         </is>
       </c>
     </row>
